--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$125</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3587" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3936" uniqueCount="394">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -553,6 +553,132 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ObservationType</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -563,10 +689,6 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
-  </si>
-  <si>
     <t>Description narrative</t>
   </si>
   <si>
@@ -716,123 +838,34 @@
     <t>Observation.statusCode.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
     <t>completed</t>
   </si>
   <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>Observation.statusCode.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
-  </si>
-  <si>
     <t>Observation.statusCode.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.effectiveTime</t>
@@ -1525,7 +1558,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK114"/>
+  <dimension ref="A1:AK125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.26171875" customWidth="true" bestFit="true"/>
@@ -4844,7 +4877,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -4863,7 +4896,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -5158,7 +5191,9 @@
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5175,10 +5210,12 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
+      <c r="M36" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5204,13 +5241,11 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>74</v>
@@ -5228,7 +5263,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>175</v>
+        <v>89</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5248,16 +5283,18 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E37" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
@@ -5274,13 +5311,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5331,7 +5366,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5349,28 +5384,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5379,11 +5414,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5410,11 +5445,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5432,7 +5469,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5452,17 +5489,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5480,11 +5517,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5511,11 +5548,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>184</v>
+        <v>74</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5533,7 +5572,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5553,17 +5592,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>80</v>
@@ -5581,7 +5620,7 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
@@ -5654,7 +5693,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>191</v>
       </c>
@@ -5669,13 +5708,13 @@
         <v>192</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5684,7 +5723,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
@@ -5715,29 +5754,31 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5757,18 +5798,16 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" t="s" s="2">
-        <v>197</v>
-      </c>
+      <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5785,11 +5824,11 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5840,7 +5879,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5860,18 +5899,16 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -5888,11 +5925,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5919,11 +5956,13 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>203</v>
+        <v>74</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5941,7 +5980,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5961,16 +6000,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
@@ -5987,10 +6028,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>85</v>
+        <v>204</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6016,29 +6059,31 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6058,21 +6103,23 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -6084,17 +6131,13 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L45" t="s" s="2">
         <v>209</v>
       </c>
+      <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>211</v>
-      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>74</v>
@@ -6143,46 +6186,46 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6191,11 +6234,11 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6246,13 +6289,13 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>74</v>
@@ -6266,18 +6309,16 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>219</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
@@ -6294,12 +6335,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6349,7 +6388,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6369,10 +6408,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6395,13 +6434,13 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6428,11 +6467,13 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6450,7 +6491,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6470,10 +6511,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6571,17 +6612,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>62</v>
+        <v>222</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6603,7 +6644,7 @@
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6615,7 +6656,7 @@
         <v>74</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>74</v>
@@ -6630,13 +6671,11 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6654,7 +6693,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6674,23 +6713,23 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6702,11 +6741,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6757,7 +6796,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6777,23 +6816,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -6805,11 +6844,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6836,13 +6875,11 @@
         <v>74</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>74</v>
+        <v>234</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>74</v>
@@ -6860,7 +6897,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6880,23 +6917,23 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -6908,11 +6945,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6963,7 +7000,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6983,23 +7020,23 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
@@ -7011,11 +7048,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7042,13 +7079,11 @@
         <v>74</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>74</v>
+        <v>243</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>74</v>
@@ -7066,7 +7101,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7086,10 +7121,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7112,12 +7147,10 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>248</v>
+        <v>85</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" t="s" s="2">
-        <v>249</v>
-      </c>
+      <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7143,13 +7176,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7167,7 +7198,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7187,10 +7218,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7215,11 +7246,15 @@
       <c r="K56" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L56" s="2"/>
+      <c r="L56" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="M56" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>74</v>
@@ -7268,55 +7303,55 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>254</v>
-      </c>
       <c r="B57" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E57" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K57" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
@@ -7407,7 +7442,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -7419,11 +7454,11 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>260</v>
+        <v>204</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7474,59 +7509,59 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="B59" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" t="s" s="2">
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L59" s="2"/>
-      <c r="M59" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7553,13 +7588,11 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>74</v>
+        <v>265</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7577,44 +7610,46 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>267</v>
-      </c>
       <c r="B60" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F60" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>74</v>
@@ -7623,13 +7658,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>269</v>
+        <v>86</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7656,13 +7689,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7680,7 +7711,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>267</v>
+        <v>89</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7700,16 +7731,18 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E61" s="2"/>
+      <c r="E61" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
@@ -7726,10 +7759,12 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>271</v>
+        <v>85</v>
       </c>
       <c r="L61" s="2"/>
-      <c r="M61" s="2"/>
+      <c r="M61" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7740,7 +7775,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>74</v>
+        <v>268</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7755,11 +7790,13 @@
         <v>74</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>272</v>
+        <v>74</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -7777,7 +7814,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7797,21 +7834,23 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E62" s="2"/>
+      <c r="E62" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -7823,10 +7862,12 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>274</v>
+        <v>112</v>
       </c>
       <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
+      <c r="M62" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7876,7 +7917,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>273</v>
+        <v>182</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7896,21 +7937,23 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -7922,10 +7965,12 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
+      <c r="M63" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -7951,11 +7996,13 @@
         <v>74</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>276</v>
+        <v>74</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -7973,7 +8020,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>275</v>
+        <v>186</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7991,26 +8038,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E64" s="2"/>
+      <c r="E64" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="F64" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -8019,13 +8068,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>279</v>
+        <v>189</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8076,13 +8123,13 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>277</v>
+        <v>190</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>74</v>
@@ -8094,26 +8141,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E65" s="2"/>
+      <c r="E65" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
@@ -8122,13 +8171,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>281</v>
+        <v>193</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8155,11 +8202,13 @@
         <v>74</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>282</v>
+        <v>74</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8177,13 +8226,13 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>280</v>
+        <v>194</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>74</v>
@@ -8197,10 +8246,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8211,7 +8260,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -8223,10 +8272,12 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>271</v>
+        <v>196</v>
       </c>
       <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
+      <c r="M66" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8252,11 +8303,13 @@
         <v>74</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>284</v>
+        <v>74</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -8274,13 +8327,13 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>283</v>
+        <v>198</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>74</v>
@@ -8292,12 +8345,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8311,7 +8364,7 @@
         <v>75</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>74</v>
@@ -8320,13 +8373,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>286</v>
+        <v>200</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8377,13 +8428,13 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>285</v>
+        <v>201</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>74</v>
@@ -8397,21 +8448,23 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E68" s="2"/>
+      <c r="E68" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -8423,10 +8476,12 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>288</v>
+        <v>204</v>
       </c>
       <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
+      <c r="M68" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8476,7 +8531,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>287</v>
+        <v>206</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8496,21 +8551,23 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E69" s="2"/>
+      <c r="E69" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -8522,10 +8579,12 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
+      <c r="M69" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8575,7 +8634,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>289</v>
+        <v>211</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8595,21 +8654,23 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" s="2"/>
+      <c r="E70" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>74</v>
@@ -8621,10 +8682,12 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>292</v>
+        <v>170</v>
       </c>
       <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
+      <c r="M70" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8674,7 +8737,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>291</v>
+        <v>215</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8692,12 +8755,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8711,7 +8774,7 @@
         <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>74</v>
@@ -8720,13 +8783,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8777,13 +8840,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8797,10 +8860,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8811,7 +8874,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>74</v>
@@ -8823,7 +8886,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8852,13 +8915,11 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>74</v>
+        <v>283</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8876,13 +8937,13 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>74</v>
@@ -8896,10 +8957,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8910,7 +8971,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>74</v>
@@ -8922,7 +8983,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8975,13 +9036,13 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>74</v>
@@ -8993,12 +9054,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9009,10 +9070,10 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>74</v>
@@ -9021,14 +9082,10 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9054,13 +9111,11 @@
         <v>74</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>74</v>
+        <v>287</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>74</v>
@@ -9078,13 +9133,13 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>74</v>
@@ -9096,28 +9151,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>74</v>
@@ -9126,11 +9179,13 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L75" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="M75" t="s" s="2">
-        <v>86</v>
+        <v>290</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9157,11 +9212,13 @@
         <v>74</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>74</v>
@@ -9179,13 +9236,13 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>89</v>
+        <v>288</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>74</v>
@@ -9197,12 +9254,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9213,10 +9270,10 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>74</v>
@@ -9225,11 +9282,13 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L76" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="M76" t="s" s="2">
-        <v>92</v>
+        <v>292</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9256,13 +9315,11 @@
         <v>74</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>74</v>
+        <v>293</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>74</v>
@@ -9280,7 +9337,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>93</v>
+        <v>291</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9300,10 +9357,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9314,7 +9371,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>74</v>
@@ -9326,12 +9383,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>95</v>
+        <v>282</v>
       </c>
       <c r="L77" s="2"/>
-      <c r="M77" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9357,13 +9412,11 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
-        <v>74</v>
+        <v>295</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
@@ -9381,38 +9434,36 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>97</v>
+        <v>294</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E78" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
@@ -9420,7 +9471,7 @@
         <v>75</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>74</v>
@@ -9429,11 +9480,13 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L78" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="M78" t="s" s="2">
-        <v>86</v>
+        <v>297</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9460,11 +9513,13 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9482,13 +9537,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>89</v>
+        <v>296</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9502,18 +9557,16 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E79" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
@@ -9530,12 +9583,10 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="L79" s="2"/>
-      <c r="M79" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9585,7 +9636,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>104</v>
+        <v>298</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9605,23 +9656,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E80" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>74</v>
@@ -9633,12 +9682,10 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>107</v>
+        <v>301</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9688,13 +9735,13 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>109</v>
+        <v>300</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>74</v>
@@ -9708,23 +9755,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E81" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>74</v>
@@ -9736,12 +9781,10 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>112</v>
+        <v>303</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9749,7 +9792,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>74</v>
@@ -9791,13 +9834,13 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>115</v>
+        <v>302</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>74</v>
@@ -9811,18 +9854,16 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E82" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>75</v>
       </c>
@@ -9839,11 +9880,13 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L82" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="M82" t="s" s="2">
-        <v>118</v>
+        <v>306</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9894,13 +9937,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>119</v>
+        <v>304</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -9914,10 +9957,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9940,12 +9983,10 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>95</v>
+        <v>308</v>
       </c>
       <c r="L83" s="2"/>
-      <c r="M83" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -9995,7 +10036,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10015,10 +10056,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10026,10 +10067,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -10041,7 +10082,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>85</v>
+        <v>310</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10055,7 +10096,7 @@
         <v>74</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>313</v>
+        <v>74</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>74</v>
@@ -10070,11 +10111,13 @@
         <v>74</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>314</v>
+        <v>74</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>74</v>
@@ -10092,13 +10135,13 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>74</v>
@@ -10110,12 +10153,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10126,10 +10169,10 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>74</v>
@@ -10138,11 +10181,13 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L85" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="M85" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10193,13 +10238,13 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -10213,16 +10258,18 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
@@ -10239,16 +10286,16 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>320</v>
+        <v>86</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
-        <v>321</v>
+        <v>74</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
@@ -10270,13 +10317,11 @@
         <v>74</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>74</v>
@@ -10294,7 +10339,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>322</v>
+        <v>89</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10314,10 +10359,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10328,7 +10373,7 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>74</v>
@@ -10340,10 +10385,12 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
+      <c r="M87" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10393,13 +10440,13 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>324</v>
+        <v>93</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>74</v>
@@ -10413,10 +10460,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10439,10 +10486,12 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>326</v>
+        <v>95</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
+      <c r="M88" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10492,7 +10541,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>327</v>
+        <v>97</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10504,7 +10553,7 @@
         <v>74</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>74</v>
@@ -10512,16 +10561,18 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E89" s="2"/>
+      <c r="E89" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
@@ -10538,10 +10589,12 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>329</v>
+        <v>85</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
+      <c r="M89" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10567,13 +10620,11 @@
         <v>74</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>74</v>
@@ -10591,7 +10642,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>330</v>
+        <v>89</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10611,16 +10662,18 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E90" s="2"/>
+      <c r="E90" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
@@ -10637,10 +10690,12 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>332</v>
+        <v>102</v>
       </c>
       <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
+      <c r="M90" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -10690,7 +10745,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>333</v>
+        <v>104</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10710,16 +10765,18 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E91" s="2"/>
+      <c r="E91" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
@@ -10736,10 +10793,12 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>335</v>
+        <v>107</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
+      <c r="M91" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -10789,7 +10848,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>336</v>
+        <v>109</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10809,18 +10868,20 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E92" s="2"/>
+      <c r="E92" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>75</v>
@@ -10835,10 +10896,12 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>338</v>
+        <v>112</v>
       </c>
       <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
+      <c r="M92" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -10846,7 +10909,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>74</v>
@@ -10888,7 +10951,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>339</v>
+        <v>115</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10908,18 +10971,20 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E93" s="2"/>
+      <c r="E93" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>75</v>
@@ -10934,10 +10999,12 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>341</v>
+        <v>102</v>
       </c>
       <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
+      <c r="M93" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -10987,7 +11054,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>342</v>
+        <v>119</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -11007,10 +11074,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11021,7 +11088,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>74</v>
@@ -11033,10 +11100,12 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>344</v>
+        <v>95</v>
       </c>
       <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
+      <c r="M94" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11086,13 +11155,13 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>345</v>
+        <v>125</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>74</v>
@@ -11106,10 +11175,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11117,7 +11186,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>75</v>
@@ -11132,7 +11201,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>347</v>
+        <v>85</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11146,7 +11215,7 @@
         <v>74</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>74</v>
@@ -11161,13 +11230,11 @@
         <v>74</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>74</v>
+        <v>325</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>74</v>
@@ -11185,10 +11252,10 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>75</v>
@@ -11205,10 +11272,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11231,10 +11298,12 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>350</v>
+        <v>107</v>
       </c>
       <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
+      <c r="M96" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11284,7 +11353,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11304,10 +11373,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11330,14 +11399,16 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>353</v>
+        <v>107</v>
       </c>
       <c r="L97" s="2"/>
-      <c r="M97" s="2"/>
+      <c r="M97" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
-        <v>74</v>
+        <v>332</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
@@ -11383,7 +11454,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11403,10 +11474,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11429,7 +11500,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>356</v>
+        <v>107</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11482,7 +11553,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11502,10 +11573,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11516,7 +11587,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>74</v>
@@ -11528,7 +11599,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11581,13 +11652,13 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>74</v>
@@ -11601,10 +11672,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11615,7 +11686,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>74</v>
@@ -11627,7 +11698,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11680,13 +11751,13 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>74</v>
@@ -11700,10 +11771,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11714,7 +11785,7 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>74</v>
@@ -11726,7 +11797,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11779,13 +11850,13 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>74</v>
@@ -11797,12 +11868,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11813,10 +11884,10 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>74</v>
@@ -11825,14 +11896,10 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -11882,13 +11949,13 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>74</v>
@@ -11902,18 +11969,16 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E103" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
@@ -11930,12 +11995,10 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>85</v>
+        <v>349</v>
       </c>
       <c r="L103" s="2"/>
-      <c r="M103" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M103" s="2"/>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -11961,11 +12024,13 @@
         <v>74</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y103" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z103" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>74</v>
@@ -11983,7 +12048,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>89</v>
+        <v>350</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12003,10 +12068,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12017,7 +12082,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>74</v>
@@ -12029,12 +12094,10 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>91</v>
+        <v>352</v>
       </c>
       <c r="L104" s="2"/>
-      <c r="M104" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M104" s="2"/>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -12084,13 +12147,13 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>93</v>
+        <v>353</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>74</v>
@@ -12104,10 +12167,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12130,12 +12193,10 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>95</v>
+        <v>355</v>
       </c>
       <c r="L105" s="2"/>
-      <c r="M105" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M105" s="2"/>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12185,7 +12246,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>97</v>
+        <v>356</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12197,7 +12258,7 @@
         <v>74</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>74</v>
@@ -12205,18 +12266,16 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E106" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
@@ -12233,12 +12292,10 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>85</v>
+        <v>358</v>
       </c>
       <c r="L106" s="2"/>
-      <c r="M106" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M106" s="2"/>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -12264,11 +12321,13 @@
         <v>74</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y106" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z106" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>74</v>
@@ -12286,7 +12345,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>89</v>
+        <v>359</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12306,18 +12365,16 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E107" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>80</v>
       </c>
@@ -12334,12 +12391,10 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>102</v>
+        <v>361</v>
       </c>
       <c r="L107" s="2"/>
-      <c r="M107" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -12389,7 +12444,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>104</v>
+        <v>362</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12409,18 +12464,16 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E108" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
@@ -12437,12 +12490,10 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>107</v>
+        <v>364</v>
       </c>
       <c r="L108" s="2"/>
-      <c r="M108" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -12492,7 +12543,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>109</v>
+        <v>365</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12512,20 +12563,18 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E109" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>75</v>
@@ -12540,12 +12589,10 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>112</v>
+        <v>367</v>
       </c>
       <c r="L109" s="2"/>
-      <c r="M109" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -12553,7 +12600,7 @@
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>74</v>
@@ -12595,7 +12642,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>115</v>
+        <v>368</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12615,23 +12662,21 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E110" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>74</v>
@@ -12643,12 +12688,10 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>102</v>
+        <v>370</v>
       </c>
       <c r="L110" s="2"/>
-      <c r="M110" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -12698,13 +12741,13 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>119</v>
+        <v>369</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>74</v>
@@ -12718,10 +12761,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12744,12 +12787,10 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>95</v>
+        <v>372</v>
       </c>
       <c r="L111" s="2"/>
-      <c r="M111" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -12799,7 +12840,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>125</v>
+        <v>371</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12819,10 +12860,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12833,7 +12874,7 @@
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>74</v>
@@ -12845,7 +12886,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>85</v>
+        <v>374</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12856,7 +12897,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>74</v>
@@ -12874,11 +12915,13 @@
         <v>74</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>378</v>
+        <v>74</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>74</v>
@@ -12896,13 +12939,13 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>74</v>
@@ -12914,12 +12957,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12927,13 +12970,13 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>74</v>
@@ -12942,10 +12985,14 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="L113" s="2"/>
-      <c r="M113" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -12995,13 +13042,13 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>74</v>
@@ -13015,21 +13062,23 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>74</v>
@@ -13041,10 +13090,12 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>382</v>
+        <v>85</v>
       </c>
       <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
+      <c r="M114" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13070,13 +13121,11 @@
         <v>74</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>74</v>
@@ -13094,26 +13143,1137 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L115" s="2"/>
+      <c r="M115" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L116" s="2"/>
+      <c r="M116" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AG114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH114" t="s" s="2">
+      <c r="B117" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L117" s="2"/>
+      <c r="M117" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y117" s="2"/>
+      <c r="Z117" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L118" s="2"/>
+      <c r="M118" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E119" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L119" s="2"/>
+      <c r="M119" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E120" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L120" s="2"/>
+      <c r="M120" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E121" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L121" s="2"/>
+      <c r="M121" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G122" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI114" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK114" t="s" s="2">
+      <c r="H122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L122" s="2"/>
+      <c r="M122" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L123" s="2"/>
+      <c r="M123" s="2"/>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y123" s="2"/>
+      <c r="Z123" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L124" s="2"/>
+      <c r="M124" s="2"/>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L125" s="2"/>
+      <c r="M125" s="2"/>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK125" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK114">
+  <autoFilter ref="A1:AK125">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13123,7 +14283,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI124">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-resultat.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-resultat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5708,7 +5708,7 @@
         <v>192</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>75</v>
